--- a/retour-secu/ig/ValueSet-vs-pdlgc-telecom-type.xlsx
+++ b/retour-secu/ig/ValueSet-vs-pdlgc-telecom-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:39:27+00:00</t>
+    <t>2026-08-28T09:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
